--- a/data/accounts.xlsx
+++ b/data/accounts.xlsx
@@ -1532,7 +1532,7 @@
       <u val="none"/>
       <vertAlign val="baseline"/>
       <sz val="10.000000"/>
-      <color indexed="64"/>
+      <color theme="1"/>
       <name val="Sans"/>
     </font>
     <font>
@@ -1542,7 +1542,6 @@
       <u val="none"/>
       <vertAlign val="baseline"/>
       <sz val="11.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1572,7 +1571,6 @@
       <u val="none"/>
       <vertAlign val="baseline"/>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1602,7 +1600,6 @@
       <u val="none"/>
       <vertAlign val="baseline"/>
       <sz val="10.500000"/>
-      <color indexed="64"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1616,37 +1613,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC9D08C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC65911"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD966"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="65"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -53980,7 +53971,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{0021007B-0024-4E52-BEC5-00E300BD002B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00DB00EE-007B-42DC-BA5C-00AC000F004B}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>INDIRECT("Permissions[permission_function]")</xm:f>
           </x14:formula1>
@@ -54166,7 +54157,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{000D00D4-00E1-44AC-A512-004C003E00A3}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{002000D1-00C5-4005-B2B9-0043008B00C8}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>INDIRECT("Roles[role_name]")</xm:f>
           </x14:formula1>
@@ -54710,25 +54701,25 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00EB0013-00BB-4104-8CBC-0010007000CE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{008D00E8-0085-462A-9D69-00B800EF00BB}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>INDIRECT("PropertyTypes[property_type]")</xm:f>
           </x14:formula1>
           <xm:sqref>E:E</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{0050001E-0032-4025-B3FD-0019007000E8}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00D50025-0072-408A-AB72-00E200890067}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>INDIRECT("Locations[location_name]")</xm:f>
           </x14:formula1>
           <xm:sqref>F:G</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{00C90063-00D2-4525-9AFA-0056000100EF}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00140039-0048-414C-9C4E-005A00D10081}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>INDIRECT("PropertyCategories[property_category_name]")</xm:f>
           </x14:formula1>
           <xm:sqref>I:I</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{005E00C9-00C0-4890-B82B-00EB00AF0010}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00FC00F9-0031-4141-8F9A-0060007C00D3}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>INDIRECT("Owners[owner_name]")</xm:f>
           </x14:formula1>
@@ -55196,13 +55187,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{007D0020-00F4-4895-A491-00E100DA0030}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{009D00D8-0055-4336-8C56-006D00B10020}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>INDIRECT("ReservableunitTypes[reservable_unit_type]")</xm:f>
           </x14:formula1>
           <xm:sqref>G1:G94</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{005A00D9-003E-416B-A457-002000390064}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00AD003E-001E-462C-BA54-00F900BA00DE}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>INDIRECT("Properties[property_name]")</xm:f>
           </x14:formula1>
